--- a/src/data/raw/2015 შუალედური ოქტომბერი საკრებულო.xlsx
+++ b/src/data/raw/2015 შუალედური ოქტომბერი საკრებულო.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Dropbox (Personal)\My projects\Elections\ge_elections_dashboard\wireframe\observable_framework\elections_data\src\data\raw\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B2FE039E-C07E-42AF-B1F8-C2E7772B53EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2951383D-4791-42BC-86CD-E7E0CB306E81}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-103" yWindow="-103" windowWidth="33120" windowHeight="18000" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="34">
   <si>
     <t>ოლქის N და დასახელება</t>
   </si>
@@ -134,6 +134,9 @@
   </si>
   <si>
     <t>41. მელორი გელანტია</t>
+  </si>
+  <si>
+    <t>maj_id</t>
   </si>
 </sst>
 </file>
@@ -547,416 +550,443 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:Q12"/>
+  <dimension ref="A1:R12"/>
   <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="15.07421875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="16.84375" customWidth="1"/>
-    <col min="3" max="3" width="10.4609375" customWidth="1"/>
-    <col min="4" max="4" width="20.07421875" customWidth="1"/>
-    <col min="5" max="5" width="22.3046875" customWidth="1"/>
-    <col min="6" max="6" width="12.53515625" customWidth="1"/>
-    <col min="7" max="7" width="12.84375" customWidth="1"/>
-    <col min="8" max="8" width="15.53515625" customWidth="1"/>
-    <col min="9" max="9" width="18.07421875" customWidth="1"/>
-    <col min="10" max="10" width="3" bestFit="1" customWidth="1"/>
-    <col min="11" max="13" width="4" bestFit="1" customWidth="1"/>
-    <col min="14" max="15" width="4" customWidth="1"/>
-    <col min="16" max="16" width="10.3046875" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="0" hidden="1" customWidth="1"/>
+    <col min="2" max="2" width="15.07421875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="16.84375" customWidth="1"/>
+    <col min="4" max="4" width="10.4609375" customWidth="1"/>
+    <col min="5" max="5" width="20.07421875" customWidth="1"/>
+    <col min="6" max="6" width="22.3046875" customWidth="1"/>
+    <col min="7" max="7" width="12.53515625" customWidth="1"/>
+    <col min="8" max="8" width="12.84375" customWidth="1"/>
+    <col min="9" max="9" width="15.53515625" customWidth="1"/>
+    <col min="10" max="10" width="18.07421875" customWidth="1"/>
+    <col min="11" max="11" width="3" bestFit="1" customWidth="1"/>
+    <col min="12" max="14" width="4" bestFit="1" customWidth="1"/>
+    <col min="15" max="16" width="4" customWidth="1"/>
+    <col min="17" max="17" width="10.3046875" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="0" hidden="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" ht="47.6" x14ac:dyDescent="0.4">
-      <c r="A1" s="4" t="s">
+    <row r="1" spans="1:18" ht="47.6" x14ac:dyDescent="0.4">
+      <c r="A1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B1" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="4" t="s">
+      <c r="C1" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="C1" s="4" t="s">
+      <c r="D1" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="4" t="s">
+      <c r="E1" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="4" t="s">
+      <c r="F1" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="F1" s="4" t="s">
+      <c r="G1" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="4" t="s">
+      <c r="H1" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="H1" s="4" t="s">
+      <c r="I1" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="I1" s="4" t="s">
+      <c r="J1" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="J1" s="5" t="s">
+      <c r="K1" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="K1" s="5" t="s">
+      <c r="L1" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="L1" s="5" t="s">
+      <c r="M1" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="M1" s="5" t="s">
+      <c r="N1" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="N1" s="5" t="s">
+      <c r="O1" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="O1" s="5" t="s">
+      <c r="P1" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="P1" s="4" t="s">
+      <c r="Q1" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="Q1" s="5" t="s">
+      <c r="R1" s="5" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:17" ht="15.9" x14ac:dyDescent="0.5">
-      <c r="A2" s="3">
+    <row r="2" spans="1:18" ht="15.9" x14ac:dyDescent="0.5">
+      <c r="A2">
+        <v>1112</v>
+      </c>
+      <c r="B2" s="3">
         <v>11</v>
       </c>
-      <c r="B2" s="1">
+      <c r="C2" s="1">
         <v>12</v>
       </c>
-      <c r="C2" s="1">
+      <c r="D2" s="1">
         <v>28</v>
       </c>
-      <c r="D2" s="1">
+      <c r="E2" s="1">
         <v>788</v>
       </c>
-      <c r="E2" s="1">
+      <c r="F2" s="1">
         <v>2</v>
       </c>
-      <c r="F2" s="1">
+      <c r="G2" s="1">
         <v>130</v>
       </c>
-      <c r="G2" s="1">
+      <c r="H2" s="1">
         <v>344</v>
       </c>
-      <c r="H2" s="1">
+      <c r="I2" s="1">
         <v>451</v>
       </c>
-      <c r="I2" s="1">
+      <c r="J2" s="1">
         <v>750</v>
       </c>
-      <c r="J2" s="1">
+      <c r="K2" s="1">
         <v>10</v>
       </c>
-      <c r="K2" s="1">
+      <c r="L2" s="1">
         <v>139</v>
       </c>
-      <c r="L2" s="1">
+      <c r="M2" s="1">
         <v>171</v>
       </c>
-      <c r="M2" s="1">
+      <c r="N2" s="1">
         <v>106</v>
       </c>
-      <c r="N2" s="1"/>
       <c r="O2" s="1"/>
-      <c r="P2" s="1">
+      <c r="P2" s="1"/>
+      <c r="Q2" s="1">
         <v>23</v>
       </c>
-      <c r="Q2" s="7">
-        <f>P2*100/H2</f>
+      <c r="R2" s="7">
+        <f>Q2*100/I2</f>
         <v>5.0997782705099777</v>
       </c>
     </row>
-    <row r="3" spans="1:17" ht="15.9" x14ac:dyDescent="0.5">
-      <c r="A3" s="3">
+    <row r="3" spans="1:18" ht="15.9" x14ac:dyDescent="0.5">
+      <c r="A3">
+        <v>1112</v>
+      </c>
+      <c r="B3" s="3">
         <v>11</v>
       </c>
-      <c r="B3" s="1">
+      <c r="C3" s="1">
         <v>12</v>
       </c>
-      <c r="C3" s="1">
+      <c r="D3" s="1">
         <v>29</v>
       </c>
-      <c r="D3" s="1">
+      <c r="E3" s="1">
         <v>749</v>
       </c>
-      <c r="E3" s="1">
+      <c r="F3" s="1">
         <v>2</v>
       </c>
-      <c r="F3" s="1">
+      <c r="G3" s="1">
         <v>171</v>
       </c>
-      <c r="G3" s="1">
+      <c r="H3" s="1">
         <v>396</v>
       </c>
-      <c r="H3" s="1">
+      <c r="I3" s="1">
         <v>485</v>
       </c>
-      <c r="I3" s="1">
+      <c r="J3" s="1">
         <v>700</v>
       </c>
-      <c r="J3" s="1">
+      <c r="K3" s="1">
         <v>21</v>
       </c>
-      <c r="K3" s="1">
+      <c r="L3" s="1">
         <v>30</v>
       </c>
-      <c r="L3" s="1">
+      <c r="M3" s="1">
         <v>226</v>
       </c>
-      <c r="M3" s="1">
+      <c r="N3" s="1">
         <v>179</v>
       </c>
-      <c r="N3" s="1"/>
       <c r="O3" s="1"/>
-      <c r="P3" s="1">
+      <c r="P3" s="1"/>
+      <c r="Q3" s="1">
         <v>24</v>
       </c>
-      <c r="Q3" s="7">
-        <f>P3*100/H3</f>
+      <c r="R3" s="7">
+        <f>Q3*100/I3</f>
         <v>4.9484536082474229</v>
       </c>
     </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.4">
-      <c r="A4" s="1">
+    <row r="4" spans="1:18" x14ac:dyDescent="0.4">
+      <c r="A4">
+        <v>2406</v>
+      </c>
+      <c r="B4" s="1">
         <v>24</v>
       </c>
-      <c r="B4" s="1">
+      <c r="C4" s="1">
         <v>6</v>
       </c>
-      <c r="C4" s="1">
+      <c r="D4" s="1">
         <v>16</v>
       </c>
-      <c r="D4" s="1">
+      <c r="E4" s="1">
         <v>478</v>
       </c>
-      <c r="E4" s="1">
+      <c r="F4" s="1">
         <v>0</v>
       </c>
-      <c r="F4" s="1">
+      <c r="G4" s="1">
         <v>32</v>
       </c>
-      <c r="G4" s="1">
+      <c r="H4" s="1">
         <v>100</v>
       </c>
-      <c r="H4" s="1">
+      <c r="I4" s="1">
         <v>142</v>
       </c>
-      <c r="I4" s="1">
+      <c r="J4" s="1">
         <v>500</v>
       </c>
-      <c r="L4" s="1">
+      <c r="M4" s="1">
         <v>135</v>
       </c>
-      <c r="P4" s="1">
+      <c r="Q4" s="1">
         <v>7</v>
       </c>
     </row>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.4">
-      <c r="A5" s="1">
+    <row r="5" spans="1:18" x14ac:dyDescent="0.4">
+      <c r="A5">
+        <v>2406</v>
+      </c>
+      <c r="B5" s="1">
         <v>24</v>
       </c>
-      <c r="B5" s="1">
+      <c r="C5" s="1">
         <v>6</v>
       </c>
-      <c r="C5" s="1">
+      <c r="D5" s="1">
         <v>17</v>
       </c>
-      <c r="D5" s="1">
+      <c r="E5" s="1">
         <v>678</v>
       </c>
-      <c r="E5" s="1">
+      <c r="F5" s="1">
         <v>0</v>
       </c>
-      <c r="F5" s="1">
+      <c r="G5" s="1">
         <v>40</v>
       </c>
-      <c r="G5" s="1">
+      <c r="H5" s="1">
         <v>160</v>
       </c>
-      <c r="H5" s="1">
+      <c r="I5" s="1">
         <v>222</v>
       </c>
-      <c r="I5" s="1">
+      <c r="J5" s="1">
         <v>650</v>
       </c>
-      <c r="L5" s="1">
+      <c r="M5" s="1">
         <v>221</v>
       </c>
-      <c r="P5" s="1">
+      <c r="Q5" s="1">
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.4">
-      <c r="A6" s="1">
+    <row r="6" spans="1:18" x14ac:dyDescent="0.4">
+      <c r="A6">
+        <v>2406</v>
+      </c>
+      <c r="B6" s="1">
         <v>24</v>
       </c>
-      <c r="B6" s="1">
+      <c r="C6" s="1">
         <v>6</v>
       </c>
-      <c r="C6" s="1">
+      <c r="D6" s="1">
         <v>18</v>
       </c>
-      <c r="D6" s="1">
+      <c r="E6" s="1">
         <v>131</v>
       </c>
-      <c r="E6" s="1">
+      <c r="F6" s="1">
         <v>4</v>
       </c>
-      <c r="F6" s="1">
+      <c r="G6" s="1">
         <v>43</v>
       </c>
-      <c r="G6" s="1">
+      <c r="H6" s="1">
         <v>62</v>
       </c>
-      <c r="H6" s="1">
+      <c r="I6" s="1">
         <v>70</v>
       </c>
-      <c r="I6" s="1">
+      <c r="J6" s="1">
         <v>150</v>
       </c>
-      <c r="L6" s="1">
+      <c r="M6" s="1">
         <v>68</v>
       </c>
-      <c r="P6" s="1">
+      <c r="Q6" s="1">
         <v>2</v>
       </c>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.4">
-      <c r="A7" s="1">
+    <row r="7" spans="1:18" x14ac:dyDescent="0.4">
+      <c r="A7">
+        <v>2406</v>
+      </c>
+      <c r="B7" s="1">
         <v>24</v>
       </c>
-      <c r="B7" s="1">
+      <c r="C7" s="1">
         <v>6</v>
       </c>
-      <c r="C7" s="1">
+      <c r="D7" s="1">
         <v>49</v>
       </c>
-      <c r="D7" s="1">
+      <c r="E7" s="1">
         <v>334</v>
       </c>
-      <c r="E7" s="1">
+      <c r="F7" s="1">
         <v>1</v>
       </c>
-      <c r="F7" s="1">
+      <c r="G7" s="1">
         <v>34</v>
       </c>
-      <c r="G7" s="1">
+      <c r="H7" s="1">
         <v>113</v>
       </c>
-      <c r="H7" s="1">
+      <c r="I7" s="1">
         <v>133</v>
       </c>
-      <c r="I7" s="1">
+      <c r="J7" s="1">
         <v>350</v>
       </c>
-      <c r="L7" s="1">
+      <c r="M7" s="1">
         <v>129</v>
       </c>
-      <c r="P7" s="1">
+      <c r="Q7" s="1">
         <v>4</v>
       </c>
     </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.4">
-      <c r="A8" s="1">
+    <row r="8" spans="1:18" x14ac:dyDescent="0.4">
+      <c r="A8">
+        <v>5307</v>
+      </c>
+      <c r="B8" s="1">
         <v>53</v>
       </c>
-      <c r="B8" s="1">
+      <c r="C8" s="1">
         <v>7</v>
       </c>
-      <c r="C8" s="1">
+      <c r="D8" s="1">
         <v>10</v>
       </c>
-      <c r="D8" s="1">
+      <c r="E8" s="1">
         <v>1175</v>
       </c>
-      <c r="E8" s="1">
+      <c r="F8" s="1">
         <v>0</v>
       </c>
-      <c r="F8" s="1">
+      <c r="G8" s="1">
         <v>247</v>
       </c>
-      <c r="G8" s="1">
+      <c r="H8" s="1">
         <v>475</v>
       </c>
-      <c r="H8" s="1">
+      <c r="I8" s="1">
         <v>559</v>
       </c>
-      <c r="I8" s="1">
+      <c r="J8" s="1">
         <v>1100</v>
       </c>
-      <c r="L8" s="1">
+      <c r="M8" s="1">
         <v>367</v>
       </c>
-      <c r="N8" s="1">
+      <c r="O8" s="1">
         <v>4</v>
       </c>
-      <c r="O8" s="1">
+      <c r="P8" s="1">
         <v>160</v>
       </c>
-      <c r="P8" s="1">
+      <c r="Q8" s="1">
         <v>28</v>
       </c>
     </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.4">
-      <c r="A9" s="1">
+    <row r="9" spans="1:18" x14ac:dyDescent="0.4">
+      <c r="A9">
+        <v>6606</v>
+      </c>
+      <c r="B9" s="1">
         <v>66</v>
       </c>
-      <c r="B9" s="1">
+      <c r="C9" s="1">
         <v>6</v>
       </c>
-      <c r="C9" s="1">
+      <c r="D9" s="1">
         <v>8</v>
       </c>
-      <c r="D9" s="1">
+      <c r="E9" s="1">
         <v>822</v>
       </c>
-      <c r="E9" s="1">
+      <c r="F9" s="1">
         <v>0</v>
       </c>
-      <c r="F9" s="1">
+      <c r="G9" s="1">
         <v>165</v>
       </c>
-      <c r="G9" s="1">
+      <c r="H9" s="1">
         <v>365</v>
       </c>
-      <c r="H9" s="1">
+      <c r="I9" s="1">
         <v>445</v>
       </c>
-      <c r="I9" s="1">
+      <c r="J9" s="1">
         <v>750</v>
       </c>
-      <c r="K9" s="1">
+      <c r="L9" s="1">
         <v>115</v>
       </c>
-      <c r="L9" s="1">
+      <c r="M9" s="1">
         <v>318</v>
       </c>
-      <c r="N9" s="7"/>
-      <c r="P9" s="1">
+      <c r="O9" s="7"/>
+      <c r="Q9" s="1">
         <v>12</v>
       </c>
     </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.4">
-      <c r="A10" s="2"/>
-    </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.4">
-      <c r="A11" s="2"/>
-    </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.4">
-      <c r="A12" s="6"/>
+    <row r="10" spans="1:18" x14ac:dyDescent="0.4">
+      <c r="B10" s="2"/>
+    </row>
+    <row r="11" spans="1:18" x14ac:dyDescent="0.4">
+      <c r="B11" s="2"/>
+    </row>
+    <row r="12" spans="1:18" x14ac:dyDescent="0.4">
+      <c r="B12" s="6"/>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="A2:A3">
+  <conditionalFormatting sqref="B2:B3">
     <cfRule type="expression" dxfId="5" priority="5">
-      <formula>$B2="ჯამი"</formula>
+      <formula>$C2="ჯამი"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B2:P3 P4:P7 L4:L8 A4:I9 N8:P8 K9:L9 P9">
+  <conditionalFormatting sqref="C2:Q3 Q4:Q7 M4:M8 B4:J9 O8:Q8 L9:M9 Q9">
     <cfRule type="expression" dxfId="4" priority="6">
-      <formula>$C2="ჯამი"</formula>
+      <formula>$D2="ჯამი"</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.17" right="0.17" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -966,10 +996,10 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{251015E9-A018-425D-ADD0-9D8E04BFCB10}">
-  <dimension ref="A1:D11"/>
+  <dimension ref="A1:E11"/>
   <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
   <sheetData>
-    <row r="1" spans="1:4" ht="79.3" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:5" ht="79.3" x14ac:dyDescent="0.4">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
@@ -982,8 +1012,11 @@
       <c r="D1" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="2" spans="1:4" ht="15.9" x14ac:dyDescent="0.5">
+      <c r="E1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" ht="15.9" x14ac:dyDescent="0.5">
       <c r="A2" s="3">
         <v>11</v>
       </c>
@@ -996,8 +1029,12 @@
       <c r="D2" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="3" spans="1:4" ht="15.9" x14ac:dyDescent="0.5">
+      <c r="E2">
+        <f>A2*100+B2</f>
+        <v>1112</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" ht="15.9" x14ac:dyDescent="0.5">
       <c r="A3" s="3">
         <v>11</v>
       </c>
@@ -1010,8 +1047,12 @@
       <c r="D3" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="4" spans="1:4" ht="15.9" x14ac:dyDescent="0.5">
+      <c r="E3">
+        <f t="shared" ref="E3:E11" si="0">A3*100+B3</f>
+        <v>1112</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" ht="15.9" x14ac:dyDescent="0.5">
       <c r="A4" s="3">
         <v>11</v>
       </c>
@@ -1024,8 +1065,12 @@
       <c r="D4" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="5" spans="1:4" ht="15.9" x14ac:dyDescent="0.5">
+      <c r="E4">
+        <f t="shared" si="0"/>
+        <v>1112</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" ht="15.9" x14ac:dyDescent="0.5">
       <c r="A5" s="3">
         <v>11</v>
       </c>
@@ -1038,8 +1083,12 @@
       <c r="D5" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="E5">
+        <f t="shared" si="0"/>
+        <v>1112</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A6" s="1">
         <v>24</v>
       </c>
@@ -1052,8 +1101,12 @@
       <c r="D6" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="E6">
+        <f t="shared" si="0"/>
+        <v>2406</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A7" s="1">
         <v>53</v>
       </c>
@@ -1066,8 +1119,12 @@
       <c r="D7" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="E7">
+        <f t="shared" si="0"/>
+        <v>5307</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A8" s="1">
         <v>53</v>
       </c>
@@ -1080,8 +1137,12 @@
       <c r="D8" t="s">
         <v>29</v>
       </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="E8">
+        <f t="shared" si="0"/>
+        <v>5307</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A9" s="1">
         <v>53</v>
       </c>
@@ -1094,8 +1155,12 @@
       <c r="D9" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="E9">
+        <f t="shared" si="0"/>
+        <v>5307</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A10" s="1">
         <v>66</v>
       </c>
@@ -1108,8 +1173,12 @@
       <c r="D10" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="E10">
+        <f t="shared" si="0"/>
+        <v>6606</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A11" s="1">
         <v>66</v>
       </c>
@@ -1121,6 +1190,10 @@
       </c>
       <c r="D11" t="s">
         <v>32</v>
+      </c>
+      <c r="E11">
+        <f t="shared" si="0"/>
+        <v>6606</v>
       </c>
     </row>
   </sheetData>
@@ -1129,19 +1202,19 @@
       <formula>$B2="ჯამი"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B2:B5">
-    <cfRule type="expression" dxfId="2" priority="3">
-      <formula>$C2="ჯამი"</formula>
-    </cfRule>
-  </conditionalFormatting>
   <conditionalFormatting sqref="A6:B9">
-    <cfRule type="expression" dxfId="1" priority="7">
+    <cfRule type="expression" dxfId="2" priority="7">
       <formula>$C4="ჯამი"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A10:B11">
-    <cfRule type="expression" dxfId="0" priority="9">
+    <cfRule type="expression" dxfId="1" priority="9">
       <formula>$C6="ჯამი"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B2:B5">
+    <cfRule type="expression" dxfId="0" priority="3">
+      <formula>$C2="ჯამი"</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
